--- a/human_resources_surveys/032_corporate_diversity_training_feedback_survey--human_resources_surveys.xlsx
+++ b/human_resources_surveys/032_corporate_diversity_training_feedback_survey--human_resources_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'in-person'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'Label': 'In-Person'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'online'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'Label': 'Online'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'both'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'Label': 'Both'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'highly_likely'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'Label': 'Highly Likely'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'Label': 'Somewhat Likely'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'Label': 'Not Likely'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'hr'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'Label': 'HR'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'marketing'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'Label': 'Marketing'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'sales'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'Label': 'Sales'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'finance'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'Label': 'Finance'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'it'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'Label': 'IT'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'operations'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'Label': 'Operations'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'Label': 'Other'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'1-10'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'Label': '1-10'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'11-20'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'Label': '11-20'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'21-50'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'Label': '21-50'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'51-100'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'Label': '51-100'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_100'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'Label': 'More than 100'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'google_forms'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'Label': 'Google Forms'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'microsoft_forms'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'Label': 'Microsoft Forms'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'jotform'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'Label': 'Jotform'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'diversity,_equity_and_inclusion'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'Label': 'Diversity, Equity and Inclusion'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'team_building'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'Label': 'Team Building'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'leadership_development'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'Label': 'Leadership Development'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'all_of_the_above'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'Label': 'All of the Above'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'Label': 'Other'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'more_hands-on_exercises'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'Label': 'More hands-on exercises'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'smaller_class_size'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'Label': 'Smaller class size'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'more_interactive_elements'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'Label': 'More interactive elements'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'less_theory,_more_practice'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'Label': 'Less theory, more practice'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'Label': 'Other'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'Label': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'Label': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
